--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +769,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128766554</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>728664</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7112622</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675935</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675935</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675935</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675935</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675935</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128766554</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128675935</v>
+        <v>128766554</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>728699</v>
+        <v>728664</v>
       </c>
       <c r="R2" t="n">
-        <v>7112569</v>
+        <v>7112622</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128766554</v>
+        <v>128675935</v>
       </c>
       <c r="B3" t="n">
-        <v>92873</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>728664</v>
+        <v>728699</v>
       </c>
       <c r="R3" t="n">
-        <v>7112622</v>
+        <v>7112569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 44708-2025 artfynd.xlsx
+++ b/artfynd/A 44708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766554</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675935</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>